--- a/AAII_Financials/Quarterly/IGIC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IGIC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="92">
   <si>
     <t>IGIC</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -679,382 +679,433 @@
     <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>143500</v>
       </c>
       <c r="E8" s="3">
+        <v>125700</v>
+      </c>
+      <c r="F8" s="3">
+        <v>126300</v>
+      </c>
+      <c r="G8" s="3">
+        <v>128600</v>
+      </c>
+      <c r="H8" s="3">
+        <v>132900</v>
+      </c>
+      <c r="I8" s="3">
         <v>129000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="J8" s="3">
         <v>135200</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
         <v>135700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="M8" s="3">
         <v>130100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="N8" s="3">
         <v>150100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="O8" s="3">
         <v>101300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="P8" s="3">
         <v>133100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="Q8" s="3">
         <v>118100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="R8" s="3">
         <v>103600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="S8" s="3">
         <v>102800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="T8" s="3">
         <v>101300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="U8" s="3">
         <v>91100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="V8" s="3">
         <v>88000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="W8" s="3">
         <v>95900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="X8" s="3">
         <v>89500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="Y8" s="3">
         <v>86000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Z8" s="3">
         <v>78800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="AA8" s="3">
         <v>75400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="AB8" s="3">
         <v>139300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AC8" s="3">
         <v>71100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AD8" s="3">
         <v>229300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AE8" s="3">
         <v>110600</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC8" s="3">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG8" s="3">
         <v>194800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AH8" s="3">
         <v>96300</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>95500</v>
       </c>
       <c r="E9" s="3">
+        <v>73500</v>
+      </c>
+      <c r="F9" s="3">
+        <v>64500</v>
+      </c>
+      <c r="G9" s="3">
+        <v>63300</v>
+      </c>
+      <c r="H9" s="3">
+        <v>80000</v>
+      </c>
+      <c r="I9" s="3">
         <v>84900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="J9" s="3">
         <v>71800</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3">
         <v>76600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="M9" s="3">
         <v>62500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="N9" s="3">
         <v>71400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="O9" s="3">
         <v>59200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="P9" s="3">
         <v>68100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="Q9" s="3">
         <v>65300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="R9" s="3">
         <v>18200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="S9" s="3">
         <v>17600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="T9" s="3">
         <v>17100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="U9" s="3">
         <v>17300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="V9" s="3">
         <v>38300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="W9" s="3">
         <v>18600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="X9" s="3">
         <v>15900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="Y9" s="3">
         <v>13500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="Z9" s="3">
         <v>30900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="AA9" s="3">
         <v>13700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="AB9" s="3">
         <v>25900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AC9" s="3">
         <v>13600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AD9" s="3">
         <v>59400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AE9" s="3">
         <v>29300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AF9" s="3">
         <v>10700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AG9" s="3">
         <v>58800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AH9" s="3">
         <v>29200</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>48000</v>
       </c>
       <c r="E10" s="3">
+        <v>52200</v>
+      </c>
+      <c r="F10" s="3">
+        <v>61800</v>
+      </c>
+      <c r="G10" s="3">
+        <v>65300</v>
+      </c>
+      <c r="H10" s="3">
+        <v>52900</v>
+      </c>
+      <c r="I10" s="3">
         <v>44100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="J10" s="3">
         <v>63400</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3">
         <v>59100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="M10" s="3">
         <v>67600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="N10" s="3">
         <v>78800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="O10" s="3">
         <v>42100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="P10" s="3">
         <v>65000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="Q10" s="3">
         <v>52800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="R10" s="3">
         <v>85400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="S10" s="3">
         <v>85200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="T10" s="3">
         <v>84200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="U10" s="3">
         <v>73800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="V10" s="3">
         <v>49700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="W10" s="3">
         <v>77300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="X10" s="3">
         <v>73600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="Y10" s="3">
         <v>72500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Z10" s="3">
         <v>47900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="AA10" s="3">
         <v>61700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AB10" s="3">
         <v>113400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AC10" s="3">
         <v>57500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AD10" s="3">
         <v>169900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AE10" s="3">
         <v>81300</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC10" s="3">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG10" s="3">
         <v>136000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AH10" s="3">
         <v>67100</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1086,8 +1137,12 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1175,8 +1230,20 @@
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1264,8 +1331,20 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1299,11 +1378,11 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
@@ -1314,8 +1393,8 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
@@ -1324,42 +1403,54 @@
         <v>3</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="AA14" s="3">
         <v>200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="AB14" s="3">
         <v>5700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AC14" s="3">
         <v>100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AD14" s="3">
         <v>4800</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E15" s="3">
         <v>900</v>
@@ -1368,38 +1459,38 @@
         <v>900</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H15" s="3">
+        <v>900</v>
+      </c>
+      <c r="I15" s="3">
+        <v>900</v>
+      </c>
+      <c r="J15" s="3">
+        <v>900</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="M15" s="3">
         <v>600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="N15" s="3">
         <v>600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="O15" s="3">
         <v>400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="P15" s="3">
         <v>800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="Q15" s="3">
         <v>800</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1442,8 +1533,20 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1472,186 +1575,214 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>121500</v>
       </c>
       <c r="E17" s="3">
+        <v>101300</v>
+      </c>
+      <c r="F17" s="3">
+        <v>92600</v>
+      </c>
+      <c r="G17" s="3">
+        <v>89400</v>
+      </c>
+      <c r="H17" s="3">
+        <v>108300</v>
+      </c>
+      <c r="I17" s="3">
         <v>107500</v>
-      </c>
-      <c r="F17" s="3">
-        <v>96700</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="3">
-        <v>101300</v>
-      </c>
-      <c r="I17" s="3">
-        <v>86300</v>
       </c>
       <c r="J17" s="3">
         <v>96700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3">
+        <v>101300</v>
+      </c>
+      <c r="M17" s="3">
+        <v>86300</v>
+      </c>
+      <c r="N17" s="3">
+        <v>96700</v>
+      </c>
+      <c r="O17" s="3">
         <v>82500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="P17" s="3">
         <v>88800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="Q17" s="3">
         <v>83000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="R17" s="3">
         <v>91300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="S17" s="3">
         <v>72300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="T17" s="3">
         <v>71300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="U17" s="3">
         <v>64000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="V17" s="3">
         <v>76600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="W17" s="3">
         <v>79400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="X17" s="3">
         <v>79700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="Y17" s="3">
         <v>70400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Z17" s="3">
         <v>76500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="AA17" s="3">
         <v>68900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AB17" s="3">
         <v>115800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AC17" s="3">
         <v>55800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AD17" s="3">
         <v>211300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AE17" s="3">
         <v>97000</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC17" s="3">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG17" s="3">
         <v>164100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AH17" s="3">
         <v>84400</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>22000</v>
       </c>
       <c r="E18" s="3">
+        <v>24400</v>
+      </c>
+      <c r="F18" s="3">
+        <v>33700</v>
+      </c>
+      <c r="G18" s="3">
+        <v>39200</v>
+      </c>
+      <c r="H18" s="3">
+        <v>24600</v>
+      </c>
+      <c r="I18" s="3">
         <v>21500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="J18" s="3">
         <v>38500</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3">
         <v>34300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="M18" s="3">
         <v>43800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="N18" s="3">
         <v>53400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="O18" s="3">
         <v>18800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="P18" s="3">
         <v>44300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="Q18" s="3">
         <v>35100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="R18" s="3">
         <v>12300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="S18" s="3">
         <v>30500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="T18" s="3">
         <v>30000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="U18" s="3">
         <v>27100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="V18" s="3">
         <v>11400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="W18" s="3">
         <v>16500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="X18" s="3">
         <v>9800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="Y18" s="3">
         <v>15600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Z18" s="3">
         <v>2300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="AA18" s="3">
         <v>6500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="AB18" s="3">
         <v>23500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AC18" s="3">
         <v>15300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AD18" s="3">
         <v>18000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AE18" s="3">
         <v>13600</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG18" s="3">
         <v>30700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AH18" s="3">
         <v>11900</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1683,142 +1814,158 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>1000</v>
       </c>
       <c r="E20" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G20" s="3">
+        <v>6100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="I20" s="3">
         <v>-7200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="J20" s="3">
         <v>12900</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="M20" s="3">
         <v>6400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="N20" s="3">
         <v>18800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="O20" s="3">
         <v>6500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="P20" s="3">
         <v>1500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="Q20" s="3">
         <v>-1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="R20" s="3">
         <v>11600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="S20" s="3">
         <v>-7100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="T20" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="U20" s="3">
         <v>-4000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="V20" s="3">
         <v>-1900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="W20" s="3">
         <v>-900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="X20" s="3">
         <v>-1000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="Y20" s="3">
         <v>-4100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="Z20" s="3">
         <v>5200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="AA20" s="3">
         <v>3700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="AB20" s="3">
         <v>-11900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AC20" s="3">
         <v>-16800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AD20" s="3">
         <v>7300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AE20" s="3">
         <v>1500</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AH20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>21900</v>
       </c>
       <c r="E21" s="3">
+        <v>22900</v>
+      </c>
+      <c r="F21" s="3">
+        <v>31500</v>
+      </c>
+      <c r="G21" s="3">
+        <v>34000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>35600</v>
+      </c>
+      <c r="I21" s="3">
         <v>29600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="J21" s="3">
         <v>26500</v>
       </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
         <v>34300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="M21" s="3">
         <v>38000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="N21" s="3">
         <v>35300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="O21" s="3">
         <v>12700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="P21" s="3">
         <v>43600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="Q21" s="3">
         <v>37100</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1831,38 +1978,50 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3">
         <v>10100</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3">
         <v>12700</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD21" s="3">
         <v>27200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AE21" s="3">
         <v>16200</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="3">
         <v>27000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AH21" s="3">
         <v>10100</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1896,17 +2055,17 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1950,186 +2109,222 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>3</v>
+      <c r="D23" s="3">
+        <v>21000</v>
       </c>
       <c r="E23" s="3">
+        <v>22000</v>
+      </c>
+      <c r="F23" s="3">
+        <v>30600</v>
+      </c>
+      <c r="G23" s="3">
+        <v>33100</v>
+      </c>
+      <c r="H23" s="3">
+        <v>34700</v>
+      </c>
+      <c r="I23" s="3">
         <v>28700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="J23" s="3">
         <v>25700</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="3">
         <v>33600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="M23" s="3">
         <v>37400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="N23" s="3">
         <v>34600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="O23" s="3">
         <v>12300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="P23" s="3">
         <v>42800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="Q23" s="3">
         <v>36300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="R23" s="3">
         <v>23900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="S23" s="3">
         <v>23400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="T23" s="3">
         <v>21700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="U23" s="3">
         <v>23100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="V23" s="3">
         <v>9500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="W23" s="3">
         <v>15600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="X23" s="3">
         <v>8800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="Y23" s="3">
         <v>11500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Z23" s="3">
         <v>7500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="AA23" s="3">
         <v>10200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="AB23" s="3">
         <v>11600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AC23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AD23" s="3">
         <v>25300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AE23" s="3">
         <v>15100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AF23" s="3">
         <v>6500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AG23" s="3">
         <v>25600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AH23" s="3">
         <v>9400</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>100</v>
       </c>
       <c r="E24" s="3">
+        <v>300</v>
+      </c>
+      <c r="F24" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H24" s="3">
+        <v>600</v>
+      </c>
+      <c r="I24" s="3">
         <v>1400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="J24" s="3">
         <v>-4400</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
         <v>900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="M24" s="3">
         <v>-500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="N24" s="3">
         <v>1700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="O24" s="3">
         <v>1400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="P24" s="3">
         <v>2400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="Q24" s="3">
         <v>2400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="R24" s="3">
         <v>1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="S24" s="3">
         <v>800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="T24" s="3">
         <v>-300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="U24" s="3">
         <v>900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="W24" s="3">
         <v>-500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="X24" s="3">
         <v>600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="Y24" s="3">
         <v>1300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="Z24" s="3">
         <v>1000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="AA24" s="3">
         <v>700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="AB24" s="3">
         <v>400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AC24" s="3">
         <v>-600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AD24" s="3">
         <v>1700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AE24" s="3">
         <v>200</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2217,186 +2412,222 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>20900</v>
       </c>
       <c r="E26" s="3">
+        <v>21700</v>
+      </c>
+      <c r="F26" s="3">
+        <v>32300</v>
+      </c>
+      <c r="G26" s="3">
+        <v>33500</v>
+      </c>
+      <c r="H26" s="3">
+        <v>34100</v>
+      </c>
+      <c r="I26" s="3">
         <v>27300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="J26" s="3">
         <v>30100</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="3">
         <v>32800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="M26" s="3">
         <v>37900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="N26" s="3">
         <v>33000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="O26" s="3">
         <v>10900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="P26" s="3">
         <v>40500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="Q26" s="3">
         <v>33900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="R26" s="3">
         <v>22400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="S26" s="3">
         <v>22600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="T26" s="3">
         <v>22000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="U26" s="3">
         <v>22200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="V26" s="3">
         <v>9200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="W26" s="3">
         <v>16100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="X26" s="3">
         <v>8200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="Y26" s="3">
         <v>10200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Z26" s="3">
         <v>6600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="AA26" s="3">
         <v>9500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="AB26" s="3">
         <v>11200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AC26" s="3">
         <v>-900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AD26" s="3">
         <v>23600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AE26" s="3">
         <v>14900</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC26" s="3">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG26" s="3">
         <v>25500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AH26" s="3">
         <v>9400</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>20800</v>
       </c>
       <c r="E27" s="3">
+        <v>20800</v>
+      </c>
+      <c r="F27" s="3">
+        <v>32200</v>
+      </c>
+      <c r="G27" s="3">
+        <v>33500</v>
+      </c>
+      <c r="H27" s="3">
+        <v>34100</v>
+      </c>
+      <c r="I27" s="3">
         <v>26500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="J27" s="3">
         <v>30000</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="3">
         <v>31700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="M27" s="3">
         <v>37400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="N27" s="3">
         <v>31000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="O27" s="3">
         <v>10200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="P27" s="3">
         <v>37900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="Q27" s="3">
         <v>31700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="R27" s="3">
         <v>21000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="S27" s="3">
         <v>20900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="T27" s="3">
         <v>20400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="U27" s="3">
         <v>21300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="V27" s="3">
         <v>8500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="W27" s="3">
         <v>14300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="X27" s="3">
         <v>7600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="Y27" s="3">
         <v>9500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Z27" s="3">
         <v>6100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="AA27" s="3">
         <v>8900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="AB27" s="3">
         <v>10500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AC27" s="3">
         <v>-900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AD27" s="3">
         <v>23600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AE27" s="3">
         <v>14900</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC27" s="3">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG27" s="3">
         <v>25500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AH27" s="3">
         <v>9400</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2484,8 +2715,20 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2573,8 +2816,20 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2662,8 +2917,20 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2751,186 +3018,222 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-1000</v>
       </c>
       <c r="E32" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="H32" s="3">
+        <v>10100</v>
+      </c>
+      <c r="I32" s="3">
         <v>7200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="J32" s="3">
         <v>-12900</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>-700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="M32" s="3">
         <v>-6400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="N32" s="3">
         <v>-18800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="O32" s="3">
         <v>-6500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="P32" s="3">
         <v>-1500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="Q32" s="3">
         <v>1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="R32" s="3">
         <v>-11600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="S32" s="3">
         <v>7100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="T32" s="3">
         <v>8300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="U32" s="3">
         <v>4000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="V32" s="3">
         <v>1900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="W32" s="3">
         <v>900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="X32" s="3">
         <v>1000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="Y32" s="3">
         <v>4100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="Z32" s="3">
         <v>-5200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="AA32" s="3">
         <v>-3700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="AB32" s="3">
         <v>11900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AC32" s="3">
         <v>16800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AD32" s="3">
         <v>-7300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AE32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG32" s="3">
         <v>5100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AH32" s="3">
         <v>2500</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>20900</v>
       </c>
       <c r="E33" s="3">
+        <v>21700</v>
+      </c>
+      <c r="F33" s="3">
+        <v>32300</v>
+      </c>
+      <c r="G33" s="3">
+        <v>33500</v>
+      </c>
+      <c r="H33" s="3">
+        <v>34100</v>
+      </c>
+      <c r="I33" s="3">
         <v>27300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="J33" s="3">
         <v>30100</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3">
         <v>32800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="M33" s="3">
         <v>37900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="N33" s="3">
         <v>33000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="O33" s="3">
         <v>10900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="P33" s="3">
         <v>40500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="Q33" s="3">
         <v>33900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="R33" s="3">
         <v>21000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="S33" s="3">
         <v>20900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="T33" s="3">
         <v>20400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="U33" s="3">
         <v>21300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="V33" s="3">
         <v>8500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="W33" s="3">
         <v>14300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="X33" s="3">
         <v>7600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="Y33" s="3">
         <v>9500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Z33" s="3">
         <v>6100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="AA33" s="3">
         <v>8900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="AB33" s="3">
         <v>10500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AC33" s="3">
         <v>-900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AD33" s="3">
         <v>23600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AE33" s="3">
         <v>14900</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC33" s="3">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG33" s="3">
         <v>25500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AH33" s="3">
         <v>9400</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3018,191 +3321,227 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>20900</v>
       </c>
       <c r="E35" s="3">
+        <v>21700</v>
+      </c>
+      <c r="F35" s="3">
+        <v>32300</v>
+      </c>
+      <c r="G35" s="3">
+        <v>33500</v>
+      </c>
+      <c r="H35" s="3">
+        <v>34100</v>
+      </c>
+      <c r="I35" s="3">
         <v>27300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="J35" s="3">
         <v>30100</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L35" s="3">
         <v>32800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="M35" s="3">
         <v>37900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="N35" s="3">
         <v>33000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="O35" s="3">
         <v>10900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="P35" s="3">
         <v>40500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="Q35" s="3">
         <v>33900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="R35" s="3">
         <v>21000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="S35" s="3">
         <v>20900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="T35" s="3">
         <v>20400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="U35" s="3">
         <v>21300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="V35" s="3">
         <v>8500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="W35" s="3">
         <v>14300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="X35" s="3">
         <v>7600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="Y35" s="3">
         <v>9500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="Z35" s="3">
         <v>6100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="AA35" s="3">
         <v>8900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="AB35" s="3">
         <v>10500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AC35" s="3">
         <v>-900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AD35" s="3">
         <v>23600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AE35" s="3">
         <v>14900</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC35" s="3">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG35" s="3">
         <v>25500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AH35" s="3">
         <v>9400</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3234,8 +3573,12 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3267,142 +3610,158 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>3</v>
+      <c r="D41" s="3">
+        <v>197200</v>
       </c>
       <c r="E41" s="3">
+        <v>160500</v>
+      </c>
+      <c r="F41" s="3">
+        <v>186200</v>
+      </c>
+      <c r="G41" s="3">
+        <v>190700</v>
+      </c>
+      <c r="H41" s="3">
+        <v>164800</v>
+      </c>
+      <c r="I41" s="3">
         <v>103100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="J41" s="3">
         <v>155200</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3">
         <v>167600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="M41" s="3">
         <v>150200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>177000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>114800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>170400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="Q41" s="3">
         <v>156600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="R41" s="3">
         <v>260100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="S41" s="3">
         <v>246700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="T41" s="3">
         <v>213900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="U41" s="3">
         <v>175000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="V41" s="3">
         <v>242100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="W41" s="3">
         <v>224400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="X41" s="3">
         <v>180100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="Y41" s="3">
         <v>107700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Z41" s="3">
         <v>133400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="AA41" s="3">
         <v>312100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="AB41" s="3">
         <v>318700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AC41" s="3">
         <v>310700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AD41" s="3">
         <v>192500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AE41" s="3">
         <v>138300</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>37700</v>
       </c>
       <c r="E42" s="3">
+        <v>31100</v>
+      </c>
+      <c r="F42" s="3">
+        <v>31200</v>
+      </c>
+      <c r="G42" s="3">
+        <v>53300</v>
+      </c>
+      <c r="H42" s="3">
+        <v>51300</v>
+      </c>
+      <c r="I42" s="3">
         <v>107100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="J42" s="3">
         <v>89500</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>69700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="M42" s="3">
         <v>41700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="N42" s="3">
         <v>42200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="O42" s="3">
         <v>123200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="P42" s="3">
         <v>176200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="Q42" s="3">
         <v>252700</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -3445,97 +3804,121 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>354500</v>
       </c>
       <c r="E43" s="3">
+        <v>319500</v>
+      </c>
+      <c r="F43" s="3">
+        <v>276400</v>
+      </c>
+      <c r="G43" s="3">
+        <v>280800</v>
+      </c>
+      <c r="H43" s="3">
+        <v>330000</v>
+      </c>
+      <c r="I43" s="3">
         <v>311300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="J43" s="3">
         <v>256100</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3">
         <v>286500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="M43" s="3">
         <v>280100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>245200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>253000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="P43" s="3">
         <v>281900</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3">
         <v>216000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="S43" s="3">
         <v>172700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="T43" s="3">
         <v>212800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="U43" s="3">
         <v>172000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="V43" s="3">
         <v>179300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="W43" s="3">
         <v>155100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="X43" s="3">
         <v>188800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="Y43" s="3">
         <v>156100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="Z43" s="3">
         <v>166600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="AA43" s="3">
         <v>144400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="AB43" s="3">
         <v>175400</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z43" s="3">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD43" s="3">
         <v>113000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AE43" s="3">
         <v>122100</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3569,17 +3952,17 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3623,53 +4006,65 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>372100</v>
       </c>
       <c r="E45" s="3">
+        <v>367600</v>
+      </c>
+      <c r="F45" s="3">
+        <v>363100</v>
+      </c>
+      <c r="G45" s="3">
+        <v>388800</v>
+      </c>
+      <c r="H45" s="3">
+        <v>385700</v>
+      </c>
+      <c r="I45" s="3">
         <v>365100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="J45" s="3">
         <v>354300</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>324500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="M45" s="3">
         <v>318600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="N45" s="3">
         <v>332600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="O45" s="3">
         <v>314500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="P45" s="3">
         <v>293900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="Q45" s="3">
         <v>524200</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -3712,53 +4107,65 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>3</v>
+      <c r="D46" s="3">
+        <v>961500</v>
       </c>
       <c r="E46" s="3">
+        <v>878700</v>
+      </c>
+      <c r="F46" s="3">
+        <v>875600</v>
+      </c>
+      <c r="G46" s="3">
+        <v>913600</v>
+      </c>
+      <c r="H46" s="3">
+        <v>931800</v>
+      </c>
+      <c r="I46" s="3">
         <v>886600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="J46" s="3">
         <v>868100</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L46" s="3">
         <v>866300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="M46" s="3">
         <v>790600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>815000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>805500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>940300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>933500</v>
       </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3801,97 +4208,121 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>1054000</v>
       </c>
       <c r="E47" s="3">
+        <v>1066900</v>
+      </c>
+      <c r="F47" s="3">
+        <v>1103300</v>
+      </c>
+      <c r="G47" s="3">
+        <v>1071900</v>
+      </c>
+      <c r="H47" s="3">
+        <v>1049100</v>
+      </c>
+      <c r="I47" s="3">
         <v>1062200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="J47" s="3">
         <v>1048000</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>977500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="M47" s="3">
         <v>959400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="N47" s="3">
         <v>913500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="O47" s="3">
         <v>813700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="P47" s="3">
         <v>685800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="Q47" s="3">
         <v>565100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="R47" s="3">
         <v>1346100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="S47" s="3">
         <v>493100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="T47" s="3">
         <v>521100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="U47" s="3">
         <v>518900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="V47" s="3">
         <v>475900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="W47" s="3">
         <v>471500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="X47" s="3">
         <v>468300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="Y47" s="3">
         <v>464100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="Z47" s="3">
         <v>449700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="AA47" s="3">
         <v>396100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="AB47" s="3">
         <v>342200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AC47" s="3">
         <v>302600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AD47" s="3">
         <v>266800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AE47" s="3">
         <v>234100</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3902,174 +4333,198 @@
         <v>3</v>
       </c>
       <c r="F48" s="3">
+        <v>26400</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3">
         <v>30300</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3">
         <v>26100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3">
         <v>28600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="S48" s="3">
         <v>29300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="T48" s="3">
         <v>29800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="U48" s="3">
         <v>30700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="V48" s="3">
         <v>31200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="W48" s="3">
         <v>31300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="X48" s="3">
         <v>31700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="Y48" s="3">
         <v>32800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="Z48" s="3">
         <v>33200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="AA48" s="3">
         <v>34700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="AB48" s="3">
         <v>35700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AC48" s="3">
         <v>25700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AD48" s="3">
         <v>38400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AE48" s="3">
         <v>44300</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE48" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>3</v>
+      <c r="D49" s="3">
+        <v>79600</v>
       </c>
       <c r="E49" s="3">
+        <v>78100</v>
+      </c>
+      <c r="F49" s="3">
+        <v>70600</v>
+      </c>
+      <c r="G49" s="3">
+        <v>71500</v>
+      </c>
+      <c r="H49" s="3">
+        <v>73200</v>
+      </c>
+      <c r="I49" s="3">
         <v>75900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="J49" s="3">
         <v>67100</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="K49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L49" s="3">
         <v>70400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="M49" s="3">
         <v>67900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="N49" s="3">
         <v>65300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="O49" s="3">
         <v>68800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="P49" s="3">
         <v>70500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="Q49" s="3">
         <v>63900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="R49" s="3">
         <v>3600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="S49" s="3">
         <v>3800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="T49" s="3">
         <v>4000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="U49" s="3">
         <v>4000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="V49" s="3">
         <v>4300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="W49" s="3">
         <v>5100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="X49" s="3">
         <v>5500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="Y49" s="3">
         <v>5800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="Z49" s="3">
         <v>4700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="AA49" s="3">
         <v>3700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="AB49" s="3">
         <v>3700</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z49" s="3">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD49" s="3">
         <v>3900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AE49" s="3">
         <v>3300</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4157,8 +4612,20 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4246,97 +4713,121 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>76300</v>
       </c>
       <c r="E52" s="3">
+        <v>75300</v>
+      </c>
+      <c r="F52" s="3">
+        <v>20000</v>
+      </c>
+      <c r="G52" s="3">
+        <v>61500</v>
+      </c>
+      <c r="H52" s="3">
+        <v>66300</v>
+      </c>
+      <c r="I52" s="3">
         <v>61200</v>
       </c>
-      <c r="F52" s="3">
-        <v>17100</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
+        <v>17200</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3">
         <v>40000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="M52" s="3">
         <v>57000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="N52" s="3">
         <v>13900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="O52" s="3">
         <v>54400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="P52" s="3">
         <v>31900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="Q52" s="3">
         <v>53700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="R52" s="3">
         <v>5800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="S52" s="3">
         <v>6100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="T52" s="3">
         <v>4600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="U52" s="3">
         <v>2900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="V52" s="3">
         <v>500</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3">
         <v>400</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4424,97 +4915,121 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>3</v>
+      <c r="D54" s="3">
+        <v>2176900</v>
       </c>
       <c r="E54" s="3">
+        <v>2104600</v>
+      </c>
+      <c r="F54" s="3">
+        <v>2100800</v>
+      </c>
+      <c r="G54" s="3">
+        <v>2121800</v>
+      </c>
+      <c r="H54" s="3">
+        <v>2124000</v>
+      </c>
+      <c r="I54" s="3">
         <v>2090900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="J54" s="3">
         <v>2037500</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3">
         <v>1958400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="M54" s="3">
         <v>1879900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>1837900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>1747400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>1733400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="Q54" s="3">
         <v>1621500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="R54" s="3">
         <v>1580400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="S54" s="3">
         <v>1468900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="T54" s="3">
         <v>1461300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="U54" s="3">
         <v>1396800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="V54" s="3">
         <v>1451700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="W54" s="3">
         <v>1392800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="X54" s="3">
         <v>1391500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="Y54" s="3">
         <v>1265600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Z54" s="3">
         <v>1279200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="AA54" s="3">
         <v>1209200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="AB54" s="3">
         <v>1167200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AC54" s="3">
         <v>1052500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AD54" s="3">
         <v>1009100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AE54" s="3">
         <v>952700</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4546,8 +5061,12 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4579,53 +5098,57 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
+      <c r="D57" s="3">
+        <v>842900</v>
       </c>
       <c r="E57" s="3">
+        <v>825700</v>
+      </c>
+      <c r="F57" s="3">
+        <v>798300</v>
+      </c>
+      <c r="G57" s="3">
+        <v>815800</v>
+      </c>
+      <c r="H57" s="3">
+        <v>801500</v>
+      </c>
+      <c r="I57" s="3">
         <v>787900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="J57" s="3">
         <v>794200</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
         <v>741000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="M57" s="3">
         <v>720700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="N57" s="3">
         <v>712100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="O57" s="3">
         <v>691900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="P57" s="3">
         <v>685000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="Q57" s="3">
         <v>662900</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -4668,22 +5191,34 @@
       <c r="AE57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>2900</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
+        <v>1300</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -4694,8 +5229,8 @@
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -4757,142 +5292,166 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>533900</v>
       </c>
       <c r="E59" s="3">
+        <v>507500</v>
+      </c>
+      <c r="F59" s="3">
+        <v>469900</v>
+      </c>
+      <c r="G59" s="3">
+        <v>486200</v>
+      </c>
+      <c r="H59" s="3">
+        <v>521700</v>
+      </c>
+      <c r="I59" s="3">
         <v>502600</v>
       </c>
-      <c r="F59" s="3">
-        <v>465600</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
+        <v>465200</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>500400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="M59" s="3">
         <v>465100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>443500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>439700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="P59" s="3">
         <v>445600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="Q59" s="3">
         <v>412500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="R59" s="3">
         <v>1470800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="S59" s="3">
         <v>430500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="T59" s="3">
         <v>454200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="U59" s="3">
         <v>400800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="V59" s="3">
         <v>418200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="W59" s="3">
         <v>378300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="X59" s="3">
         <v>406100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="Y59" s="3">
         <v>323600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="Z59" s="3">
         <v>360700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="AA59" s="3">
         <v>328500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="AB59" s="3">
         <v>334200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AC59" s="3">
         <v>182900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AD59" s="3">
         <v>259800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AE59" s="3">
         <v>231500</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>3</v>
+      <c r="D60" s="3">
+        <v>1376800</v>
       </c>
       <c r="E60" s="3">
+        <v>1333200</v>
+      </c>
+      <c r="F60" s="3">
+        <v>1269500</v>
+      </c>
+      <c r="G60" s="3">
+        <v>1302000</v>
+      </c>
+      <c r="H60" s="3">
+        <v>1323200</v>
+      </c>
+      <c r="I60" s="3">
         <v>1290500</v>
       </c>
-      <c r="F60" s="3">
-        <v>1262700</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
+        <v>1259500</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3">
         <v>1241400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="M60" s="3">
         <v>1185800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>1155600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>1131600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>1130600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="Q60" s="3">
         <v>1075400</v>
       </c>
-      <c r="N60" s="3">
-        <v>0</v>
-      </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -4935,8 +5494,20 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4947,7 +5518,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>1400</v>
+        <v>300</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -4959,32 +5530,32 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>2100</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>3100</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4995,126 +5566,150 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>3000</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>1600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AE61" s="3">
         <v>1700</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3">
+        <v>131100</v>
       </c>
       <c r="E62" s="3">
+        <v>117800</v>
+      </c>
+      <c r="F62" s="3">
+        <v>120800</v>
+      </c>
+      <c r="G62" s="3">
+        <v>133300</v>
+      </c>
+      <c r="H62" s="3">
+        <v>138600</v>
+      </c>
+      <c r="I62" s="3">
         <v>150000</v>
       </c>
-      <c r="F62" s="3">
-        <v>118600</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
+        <v>119000</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>128700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="M62" s="3">
         <v>136900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="N62" s="3">
         <v>139700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="O62" s="3">
         <v>145700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="P62" s="3">
         <v>136000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="Q62" s="3">
         <v>115900</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
       <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3">
         <v>200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="X62" s="3">
         <v>200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="Y62" s="3">
         <v>100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="Z62" s="3">
         <v>100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="AA62" s="3">
         <v>100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="AB62" s="3">
         <v>100</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD62" s="3">
         <v>300</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5202,8 +5797,20 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5291,8 +5898,20 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5380,97 +5999,121 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>3</v>
+      <c r="D66" s="3">
+        <v>1507900</v>
       </c>
       <c r="E66" s="3">
+        <v>1451000</v>
+      </c>
+      <c r="F66" s="3">
+        <v>1390600</v>
+      </c>
+      <c r="G66" s="3">
+        <v>1435300</v>
+      </c>
+      <c r="H66" s="3">
+        <v>1461800</v>
+      </c>
+      <c r="I66" s="3">
         <v>1440500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="J66" s="3">
         <v>1382700</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3">
         <v>1370100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="M66" s="3">
         <v>1322700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>1297500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>1277300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>1266600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>1191300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="R66" s="3">
         <v>1169400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="S66" s="3">
         <v>1068600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="T66" s="3">
         <v>1067400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="U66" s="3">
         <v>1005900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="V66" s="3">
         <v>1049900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="W66" s="3">
         <v>997300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="X66" s="3">
         <v>988400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="Y66" s="3">
         <v>869600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Z66" s="3">
         <v>898200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="AA66" s="3">
         <v>829600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="AB66" s="3">
         <v>800900</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD66" s="3">
         <v>696900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AE66" s="3">
         <v>644100</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5502,8 +6145,12 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5591,8 +6238,20 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5680,8 +6339,20 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5769,8 +6440,20 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5858,97 +6541,121 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>600500</v>
       </c>
       <c r="E72" s="3">
+        <v>582800</v>
+      </c>
+      <c r="F72" s="3">
+        <v>612600</v>
+      </c>
+      <c r="G72" s="3">
+        <v>582500</v>
+      </c>
+      <c r="H72" s="3">
+        <v>551200</v>
+      </c>
+      <c r="I72" s="3">
         <v>519400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="J72" s="3">
         <v>531700</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3">
         <v>469300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="M72" s="3">
         <v>437200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="N72" s="3">
         <v>423000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>390700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="P72" s="3">
         <v>380300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="Q72" s="3">
         <v>340300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="R72" s="3">
         <v>306800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="S72" s="3">
         <v>282100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="T72" s="3">
         <v>264100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="U72" s="3">
         <v>242700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="V72" s="3">
         <v>232600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="W72" s="3">
         <v>223400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="X72" s="3">
         <v>221200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="Y72" s="3">
         <v>215700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Z72" s="3">
         <v>205000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="AA72" s="3">
         <v>198500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="AB72" s="3">
         <v>193300</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD72" s="3">
         <v>182200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AE72" s="3">
         <v>178800</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6036,8 +6743,20 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6125,8 +6844,20 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6214,97 +6945,121 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>3</v>
+      <c r="D76" s="3">
+        <v>669000</v>
       </c>
       <c r="E76" s="3">
+        <v>653600</v>
+      </c>
+      <c r="F76" s="3">
+        <v>710100</v>
+      </c>
+      <c r="G76" s="3">
+        <v>686500</v>
+      </c>
+      <c r="H76" s="3">
+        <v>662200</v>
+      </c>
+      <c r="I76" s="3">
         <v>650400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="J76" s="3">
         <v>654800</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3">
         <v>588200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="M76" s="3">
         <v>557200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>540400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>470100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>466800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>430200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="R76" s="3">
         <v>411000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="S76" s="3">
         <v>400300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="T76" s="3">
         <v>393900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="U76" s="3">
         <v>390900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="V76" s="3">
         <v>401900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="W76" s="3">
         <v>395500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="X76" s="3">
         <v>403100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="Y76" s="3">
         <v>396000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Z76" s="3">
         <v>381000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="AA76" s="3">
         <v>379600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="AB76" s="3">
         <v>366300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AC76" s="3">
         <v>344000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AD76" s="3">
         <v>312100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AE76" s="3">
         <v>308600</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6392,191 +7147,227 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>20900</v>
       </c>
       <c r="E81" s="3">
+        <v>21700</v>
+      </c>
+      <c r="F81" s="3">
+        <v>32300</v>
+      </c>
+      <c r="G81" s="3">
+        <v>33500</v>
+      </c>
+      <c r="H81" s="3">
+        <v>34100</v>
+      </c>
+      <c r="I81" s="3">
         <v>27300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="J81" s="3">
         <v>30100</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L81" s="3">
         <v>32800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="M81" s="3">
         <v>37900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="N81" s="3">
         <v>33000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="O81" s="3">
         <v>10900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="P81" s="3">
         <v>40500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="Q81" s="3">
         <v>33900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="R81" s="3">
         <v>21000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="S81" s="3">
         <v>20900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="T81" s="3">
         <v>20400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="U81" s="3">
         <v>21300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="V81" s="3">
         <v>8500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="W81" s="3">
         <v>14300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="X81" s="3">
         <v>7600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="Y81" s="3">
         <v>9500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Z81" s="3">
         <v>6100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="AA81" s="3">
         <v>8900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="AB81" s="3">
         <v>10500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AC81" s="3">
         <v>-900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AD81" s="3">
         <v>23600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AE81" s="3">
         <v>14900</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC81" s="3">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG81" s="3">
         <v>25500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AH81" s="3">
         <v>9400</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6608,8 +7399,12 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6643,17 +7438,17 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -6670,17 +7465,17 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
@@ -6697,8 +7492,20 @@
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6786,8 +7593,20 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6875,8 +7694,20 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6964,8 +7795,20 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7053,8 +7896,20 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7142,8 +7997,20 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7177,17 +8044,17 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R89" s="3">
         <v>0</v>
@@ -7204,17 +8071,17 @@
       <c r="V89" s="3">
         <v>0</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>0</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
@@ -7231,8 +8098,20 @@
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7264,8 +8143,12 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7299,17 +8182,17 @@
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -7326,17 +8209,17 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
@@ -7353,8 +8236,20 @@
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7442,8 +8337,20 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7531,8 +8438,20 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7566,17 +8485,17 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -7593,17 +8512,17 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
@@ -7620,8 +8539,20 @@
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7653,8 +8584,12 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7688,17 +8623,17 @@
       <c r="M96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7742,8 +8677,20 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7831,8 +8778,20 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7920,8 +8879,20 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8009,8 +8980,20 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8044,17 +9027,17 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
@@ -8071,17 +9054,17 @@
       <c r="V100" s="3">
         <v>0</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
@@ -8098,8 +9081,20 @@
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8133,17 +9128,17 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8160,17 +9155,17 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z101" s="3" t="s">
-        <v>3</v>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
       </c>
       <c r="AA101" s="3" t="s">
         <v>3</v>
@@ -8187,8 +9182,20 @@
       <c r="AE101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8222,17 +9229,17 @@
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R102" s="3">
         <v>0</v>
@@ -8249,17 +9256,17 @@
       <c r="V102" s="3">
         <v>0</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
+      <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>0</v>
       </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
@@ -8274,6 +9281,18 @@
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
